--- a/Result/profitability/3594.xlsx
+++ b/Result/profitability/3594.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM68"/>
+  <dimension ref="A1:AM69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.78</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05125000000000005</v>
+        <v>0.09125000000000003</v>
       </c>
       <c r="N2" t="n">
-        <v>35.53125</v>
+        <v>36.1725</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.08</v>
       </c>
       <c r="M3" t="n">
-        <v>0.17125</v>
+        <v>0.14625</v>
       </c>
       <c r="N3" t="n">
-        <v>35.48875</v>
+        <v>35.50625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.12375</v>
+        <v>0.20875</v>
       </c>
       <c r="N4" t="n">
-        <v>34.55875</v>
+        <v>34.2975</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2200000000000001</v>
+        <v>0.3025</v>
       </c>
       <c r="N5" t="n">
-        <v>33.09625</v>
+        <v>31.95375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2975</v>
+        <v>0.3062500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>31.2475</v>
+        <v>31.3075</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.11</v>
       </c>
       <c r="M7" t="n">
-        <v>0.39</v>
+        <v>0.3775000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>31.88625</v>
+        <v>31.18875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -8590,27 +8590,27 @@
         <v>44.83</v>
       </c>
       <c r="G65" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>11.21%</t>
+          <t>9.48%</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>-80</v>
       </c>
       <c r="J65" t="n">
-        <v>-25</v>
+        <v>-34</v>
       </c>
       <c r="K65" t="n">
-        <v>-16</v>
+        <v>-21</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.17</v>
+        <v>-0.22</v>
       </c>
       <c r="M65" t="n">
-        <v>0.165</v>
+        <v>0.15875</v>
       </c>
       <c r="N65" t="n">
         <v>33.41125</v>
@@ -8640,10 +8640,10 @@
         <v>114.2</v>
       </c>
       <c r="W65" t="n">
-        <v>0.06999999999999998</v>
+        <v>0.01999999999999999</v>
       </c>
       <c r="X65" t="n">
-        <v>-0.2916666666666666</v>
+        <v>-0.08333333333333326</v>
       </c>
       <c r="Y65" t="n">
         <v>7.049999999999997</v>
@@ -8652,10 +8652,10 @@
         <v>0.1866066701958708</v>
       </c>
       <c r="AA65" t="n">
-        <v>-0.58</v>
+        <v>-0.63</v>
       </c>
       <c r="AB65" t="n">
-        <v>-1.414634146341463</v>
+        <v>-1.536585365853659</v>
       </c>
       <c r="AC65" t="n">
         <v>17.97</v>
@@ -8717,7 +8717,7 @@
         <v>35.21</v>
       </c>
       <c r="G66" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -8728,13 +8728,13 @@
         <v>30</v>
       </c>
       <c r="J66" t="n">
+        <v>48</v>
+      </c>
+      <c r="K66" t="n">
         <v>40</v>
       </c>
-      <c r="K66" t="n">
-        <v>35</v>
-      </c>
       <c r="L66" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="M66" t="n">
         <v>0.165</v>
@@ -8767,10 +8767,10 @@
         <v>114.3</v>
       </c>
       <c r="W66" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="X66" t="n">
-        <v>-3.176470588235294</v>
+        <v>-2.909090909090909</v>
       </c>
       <c r="Y66" t="n">
         <v>-9.619999999999997</v>
@@ -8779,10 +8779,10 @@
         <v>-0.214588445237564</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="AB66" t="n">
-        <v>2.083333333333333</v>
+        <v>2.5</v>
       </c>
       <c r="AC66" t="n">
         <v>4.650000000000002</v>
@@ -8894,10 +8894,10 @@
         <v>114.4</v>
       </c>
       <c r="W67" t="n">
-        <v>0.17</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="X67" t="n">
-        <v>0.4594594594594597</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="Y67" t="n">
         <v>6.060000000000002</v>
@@ -9072,6 +9072,133 @@
       </c>
       <c r="AM68" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>3594</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>709</v>
+      </c>
+      <c r="D69" t="n">
+        <v>456</v>
+      </c>
+      <c r="E69" t="n">
+        <v>253</v>
+      </c>
+      <c r="F69" t="n">
+        <v>35.69</v>
+      </c>
+      <c r="G69" t="n">
+        <v>37</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>5.16%</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>9</v>
+      </c>
+      <c r="J69" t="n">
+        <v>45</v>
+      </c>
+      <c r="K69" t="n">
+        <v>42</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="N69" t="n">
+        <v>36.85375</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1</v>
+      </c>
+      <c r="P69" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0</v>
+      </c>
+      <c r="S69" t="n">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
+      </c>
+      <c r="V69" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W69" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="X69" t="n">
+        <v>-7.285714285714286</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>0.05156157925751326</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>-0.2038813294668749</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
